--- a/GC-IA-V5-OPERATING-CANON-TECHNOLOGY-CONSOLIDATED.xlsx
+++ b/GC-IA-V5-OPERATING-CANON-TECHNOLOGY-CONSOLIDATED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gc-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFC2CDE9-E4BF-4008-97AA-F9F8A1064764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E81135F-598C-4C56-B550-0815B2F432F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="22" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" firstSheet="13" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,6 @@
     <sheet name="Actual Technology Stack" sheetId="29" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -12720,7 +12719,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -12830,6 +12829,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8E8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -12963,7 +12980,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -13156,6 +13173,13 @@
     <xf numFmtId="0" fontId="23" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -13165,7 +13189,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -13190,11 +13213,17 @@
     <xf numFmtId="0" fontId="27" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13935,40 +13964,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>1479</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
     </row>
     <row r="2" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>1480</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
     </row>
     <row r="4" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -15150,46 +15179,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>1699</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
     </row>
     <row r="2" spans="1:17" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>1700</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
     </row>
     <row r="4" spans="1:17" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -15915,48 +15944,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>1892</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
     </row>
     <row r="2" spans="1:18" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>1893</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
     </row>
     <row r="4" spans="1:18" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -18678,38 +18707,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>2454</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
     </row>
     <row r="2" spans="1:13" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>2455</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
     </row>
     <row r="4" spans="1:13" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -20365,32 +20394,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>2673</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
     </row>
     <row r="2" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>2674</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="4" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -20774,36 +20803,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>2741</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
     </row>
     <row r="2" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>2742</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="4" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -21406,38 +21435,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>2871</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
     </row>
     <row r="2" spans="1:13" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>2872</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
     </row>
     <row r="4" spans="1:13" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -22001,40 +22030,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>3011</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
     </row>
     <row r="2" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>3012</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
     </row>
     <row r="4" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -22597,40 +22626,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>3140</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
     </row>
     <row r="2" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>3141</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
     </row>
     <row r="4" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -23367,34 +23396,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>3253</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
     </row>
     <row r="2" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>3254</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
     </row>
     <row r="4" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -23952,20 +23981,20 @@
       <c r="AH1" s="23"/>
     </row>
     <row r="2" spans="1:34" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
       <c r="M2" s="25"/>
       <c r="N2" s="25"/>
       <c r="O2" s="25"/>
@@ -35043,24 +35072,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>3363</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
     </row>
     <row r="2" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>3364</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="4" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -35957,32 +35986,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>3452</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>3453</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
@@ -36364,28 +36393,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>3560</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>3561</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
@@ -37166,28 +37195,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>3677</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>3678</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
@@ -41089,30 +41118,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>3738</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>3739</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
@@ -42148,28 +42177,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>3765</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>3766</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
@@ -42360,28 +42389,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>3810</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>3811</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
@@ -42643,22 +42672,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>3857</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="2" spans="1:5" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="80" t="s">
         <v>3858</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="60" t="s">
@@ -43162,24 +43191,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>3928</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
     </row>
     <row r="2" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="80" t="s">
         <v>3929</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="60" t="s">
@@ -43402,14 +43431,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="79" t="s">
+      <c r="A17" s="81" t="s">
         <v>3969</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="60" t="s">
@@ -43621,30 +43650,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="68" t="s">
         <v>4012</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="70" t="s">
         <v>4013</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
@@ -43682,7 +43711,7 @@
       <c r="B5" s="47" t="s">
         <v>4023</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="82" t="s">
         <v>4024</v>
       </c>
       <c r="D5" s="47" t="s">
@@ -43711,7 +43740,7 @@
       <c r="B6" s="47" t="s">
         <v>4032</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="82" t="s">
         <v>4033</v>
       </c>
       <c r="D6" s="47" t="s">
@@ -43740,7 +43769,7 @@
       <c r="B7" s="47" t="s">
         <v>4040</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="82" t="s">
         <v>4041</v>
       </c>
       <c r="D7" s="47" t="s">
@@ -43769,7 +43798,7 @@
       <c r="B8" s="47" t="s">
         <v>4048</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="82" t="s">
         <v>4049</v>
       </c>
       <c r="D8" s="47" t="s">
@@ -43798,7 +43827,7 @@
       <c r="B9" s="47" t="s">
         <v>4056</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="83" t="s">
         <v>4057</v>
       </c>
       <c r="D9" s="47" t="s">
@@ -43827,7 +43856,7 @@
       <c r="B10" s="47" t="s">
         <v>4065</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="83" t="s">
         <v>4066</v>
       </c>
       <c r="D10" s="47" t="s">
@@ -43856,7 +43885,7 @@
       <c r="B11" s="47" t="s">
         <v>4074</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="83" t="s">
         <v>4075</v>
       </c>
       <c r="D11" s="47" t="s">
@@ -43885,7 +43914,7 @@
       <c r="B12" s="47" t="s">
         <v>4082</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="84" t="s">
         <v>4160</v>
       </c>
       <c r="D12" s="47" t="s">
@@ -43914,7 +43943,7 @@
       <c r="B13" s="47" t="s">
         <v>4087</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="84" t="s">
         <v>4088</v>
       </c>
       <c r="D13" s="47" t="s">
@@ -43943,7 +43972,7 @@
       <c r="B14" s="47" t="s">
         <v>4096</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="84" t="s">
         <v>4097</v>
       </c>
       <c r="D14" s="47" t="s">
@@ -43972,7 +44001,7 @@
       <c r="B15" s="47" t="s">
         <v>4106</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="84" t="s">
         <v>4107</v>
       </c>
       <c r="D15" s="47" t="s">
@@ -44001,7 +44030,7 @@
       <c r="B16" s="47" t="s">
         <v>4114</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="83" t="s">
         <v>4115</v>
       </c>
       <c r="D16" s="47" t="s">
@@ -44030,7 +44059,7 @@
       <c r="B17" s="47" t="s">
         <v>4122</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="83" t="s">
         <v>4123</v>
       </c>
       <c r="D17" s="47" t="s">
@@ -44059,7 +44088,7 @@
       <c r="B18" s="47" t="s">
         <v>4130</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="83" t="s">
         <v>4131</v>
       </c>
       <c r="D18" s="47" t="s">
@@ -44088,7 +44117,7 @@
       <c r="B19" s="47" t="s">
         <v>4138</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="83" t="s">
         <v>4139</v>
       </c>
       <c r="D19" s="47" t="s">
@@ -44117,7 +44146,7 @@
       <c r="B20" s="47" t="s">
         <v>4146</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="83" t="s">
         <v>4147</v>
       </c>
       <c r="D20" s="47" t="s">
@@ -44146,7 +44175,7 @@
       <c r="B21" s="48" t="s">
         <v>4153</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="85" t="s">
         <v>4154</v>
       </c>
       <c r="D21" s="48" t="s">
@@ -44201,12 +44230,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>1084</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -44282,11 +44311,11 @@
       <c r="A10" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="73" t="s">
         <v>1101</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -44317,12 +44346,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>1103</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -44535,28 +44564,28 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="75" t="s">
         <v>1151</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
     </row>
     <row r="21" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="75" t="s">
         <v>1152</v>
       </c>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
     </row>
     <row r="22" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="75" t="s">
         <v>1153</v>
       </c>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -44588,12 +44617,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>1155</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -44722,12 +44751,12 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>1183</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
@@ -45029,12 +45058,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>1242</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -45247,13 +45276,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>1296</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -47602,11 +47631,11 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>1447</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
